--- a/DOCKERS/Docker_List_des_commandes.xlsx
+++ b/DOCKERS/Docker_List_des_commandes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a5f61b3e4cd8107/Inès_perso/M2i_administraeur_CLOUD.0.0/COURS_ALIRE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C95DB044-7351-4090-AA21-2D83AAB454C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C0EB8A5-9911-4B48-A950-CF1556985342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{21022E1D-66B6-492D-BD41-A1F00B9FA0CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="193">
   <si>
     <t>Actions</t>
   </si>
@@ -674,16 +674,25 @@
     <t>docker-compose up</t>
   </si>
   <si>
+    <t>docker-compose start</t>
+  </si>
+  <si>
     <t>démarrer les services à partir de docker compose en arrière-plan</t>
   </si>
   <si>
-    <t>docker-compose -d  up</t>
+    <t xml:space="preserve">docker-compose up -d </t>
+  </si>
+  <si>
+    <t>supprimer les services à partir d'un docker compose</t>
+  </si>
+  <si>
+    <t>docker-compose down</t>
   </si>
   <si>
     <t>arrêter les services à partir d'un docker compose</t>
   </si>
   <si>
-    <t>docker-compose down</t>
+    <t>docker-compose stop</t>
   </si>
   <si>
     <t>Pour créer un body html</t>
@@ -762,6 +771,9 @@
     <t>8080
 3000
 5000</t>
+  </si>
+  <si>
+    <t>Les ports disponibles sur les machines</t>
   </si>
 </sst>
 </file>
@@ -2206,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AD4E5A-CF54-4C09-A0E3-BB804316A17B}">
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="39.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53.5703125" style="17" customWidth="1"/>
@@ -2986,30 +2998,38 @@
     <row r="84" spans="1:3" ht="15">
       <c r="A84" s="98"/>
       <c r="B84" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="79" t="s">
+    </row>
+    <row r="85" spans="1:3" ht="15">
+      <c r="A85" s="98"/>
+      <c r="B85" s="77" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="15">
-      <c r="A85" s="99"/>
-      <c r="B85" s="77" t="s">
+      <c r="C85" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="79" t="s">
+    </row>
+    <row r="86" spans="1:3" ht="15">
+      <c r="A86" s="98"/>
+      <c r="B86" s="77" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A86" s="79"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="79"/>
-    </row>
-    <row r="87" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A87" s="79"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="79"/>
+      <c r="C86" s="79" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15">
+      <c r="A87" s="99"/>
+      <c r="B87" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="C87" s="79" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="88" spans="1:3" ht="39.75" customHeight="1">
       <c r="A88" s="79"/>
@@ -3097,9 +3117,9 @@
       <c r="C104" s="79"/>
     </row>
     <row r="105" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A105" s="37"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="37"/>
+      <c r="A105" s="79"/>
+      <c r="B105" s="77"/>
+      <c r="C105" s="79"/>
     </row>
     <row r="106" spans="1:3" ht="39.75" customHeight="1">
       <c r="A106" s="37"/>
@@ -3111,9 +3131,14 @@
       <c r="B107" s="38"/>
       <c r="C107" s="37"/>
     </row>
+    <row r="108" spans="1:3" ht="39.75" customHeight="1">
+      <c r="A108" s="37"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="37"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A83:A87"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A70:A82"/>
     <mergeCell ref="A2:A3"/>
@@ -3157,10 +3182,10 @@
     </row>
     <row r="2" spans="1:3" ht="39.75" customHeight="1">
       <c r="A2" s="89" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C2" s="91"/>
     </row>
@@ -3177,41 +3202,43 @@
     </row>
     <row r="4" spans="1:3" ht="39.75" customHeight="1">
       <c r="A4" s="89" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B4" s="90" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C4" s="91"/>
     </row>
     <row r="5" spans="1:3" ht="39.75" customHeight="1">
       <c r="A5" s="31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="39.75" customHeight="1">
       <c r="A6" s="89" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B6" s="92" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C6" s="91" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54.75" customHeight="1">
       <c r="A7" s="42" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="9"/>
+        <v>191</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="39.75" customHeight="1">
       <c r="A8" s="81"/>

--- a/DOCKERS/Docker_List_des_commandes.xlsx
+++ b/DOCKERS/Docker_List_des_commandes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a5f61b3e4cd8107/Inès_perso/M2i_administraeur_CLOUD.0.0/COURS_ALIRE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C0EB8A5-9911-4B48-A950-CF1556985342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAE32B89-063F-46EC-B6B2-51EAC5D9CEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{21022E1D-66B6-492D-BD41-A1F00B9FA0CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="197">
   <si>
     <t>Actions</t>
   </si>
@@ -693,6 +693,18 @@
   </si>
   <si>
     <t>docker-compose stop</t>
+  </si>
+  <si>
+    <t>pour transformer des commandes dockers en docker compose</t>
+  </si>
+  <si>
+    <t>https://www.composerize.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pour transformer un docker compose en commandes dockers  </t>
+  </si>
+  <si>
+    <t>https://www.decomposerize.com/</t>
   </si>
   <si>
     <t>Pour créer un body html</t>
@@ -1583,7 +1595,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1882,6 +1894,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3023,7 +3038,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" ht="15">
-      <c r="A87" s="99"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="77" t="s">
         <v>179</v>
       </c>
@@ -3031,15 +3046,23 @@
         <v>180</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A88" s="79"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="79"/>
-    </row>
-    <row r="89" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A89" s="79"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="79"/>
+    <row r="88" spans="1:3" ht="15">
+      <c r="A88" s="98"/>
+      <c r="B88" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" s="101" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="15">
+      <c r="A89" s="99"/>
+      <c r="B89" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" s="101" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="90" spans="1:3" ht="39.75" customHeight="1">
       <c r="A90" s="79"/>
@@ -3138,7 +3161,7 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="A83:A89"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A70:A82"/>
     <mergeCell ref="A2:A3"/>
@@ -3155,6 +3178,10 @@
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="A4:A5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C88" r:id="rId1" xr:uid="{B9AAD477-41F6-4BFD-B989-A1C489AFD0FC}"/>
+    <hyperlink ref="C89" r:id="rId2" xr:uid="{85ECD10D-6EA2-4A74-ACD2-0AA6253FE844}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3182,10 +3209,10 @@
     </row>
     <row r="2" spans="1:3" ht="39.75" customHeight="1">
       <c r="A2" s="89" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C2" s="91"/>
     </row>
@@ -3202,42 +3229,42 @@
     </row>
     <row r="4" spans="1:3" ht="39.75" customHeight="1">
       <c r="A4" s="89" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B4" s="90" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C4" s="91"/>
     </row>
     <row r="5" spans="1:3" ht="39.75" customHeight="1">
       <c r="A5" s="31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="39.75" customHeight="1">
       <c r="A6" s="89" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B6" s="92" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C6" s="91" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54.75" customHeight="1">
       <c r="A7" s="42" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="39.75" customHeight="1">

--- a/DOCKERS/Docker_List_des_commandes.xlsx
+++ b/DOCKERS/Docker_List_des_commandes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a5f61b3e4cd8107/Inès_perso/M2i_administraeur_CLOUD.0.0/COURS_ALIRE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAE32B89-063F-46EC-B6B2-51EAC5D9CEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{CAE32B89-063F-46EC-B6B2-51EAC5D9CEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADCA01C-0D1C-4F5F-BFBF-FFFE582A6804}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{21022E1D-66B6-492D-BD41-A1F00B9FA0CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="207">
   <si>
     <t>Actions</t>
   </si>
@@ -787,12 +787,44 @@
   <si>
     <t>Les ports disponibles sur les machines</t>
   </si>
+  <si>
+    <t>Options possibles</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>container_name</t>
+  </si>
+  <si>
+    <t>restart</t>
+  </si>
+  <si>
+    <t>volumes</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>ports</t>
+  </si>
+  <si>
+    <t>DOCKERHUB</t>
+  </si>
+  <si>
+    <t>Permet d'avoir certaines informations</t>
+  </si>
+  <si>
+    <t>CMD
+chemin absolu 
+environment</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,7 +946,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1588,6 +1620,51 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1595,7 +1672,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1730,24 +1807,147 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1763,139 +1963,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2234,15 +2332,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AD4E5A-CF54-4C09-A0E3-BB804316A17B}">
   <dimension ref="A1:C108"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="39.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.5703125" style="17" customWidth="1"/>
     <col min="2" max="2" width="89.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="122.42578125" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2252,8 +2350,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="82" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -2263,15 +2361,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="47"/>
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="83"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="23"/>
     </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="48" t="s">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="32" t="s">
@@ -2279,15 +2377,15 @@
       </c>
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="49"/>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="91"/>
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="16"/>
     </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="52" t="s">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="93" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -2297,23 +2395,23 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.75">
-      <c r="A7" s="53"/>
+    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="94"/>
       <c r="B7" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="93" t="s">
+      <c r="C7" s="74" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="54"/>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="95"/>
       <c r="B8" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="23"/>
     </row>
-    <row r="9" spans="1:3" ht="15">
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>16</v>
       </c>
@@ -2322,7 +2420,7 @@
       </c>
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3" ht="39.75" customHeight="1">
+    <row r="10" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>18</v>
       </c>
@@ -2333,7 +2431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15">
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>21</v>
       </c>
@@ -2342,8 +2440,8 @@
       </c>
       <c r="C11" s="10"/>
     </row>
-    <row r="12" spans="1:3" ht="15">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="82" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="18" t="s">
@@ -2353,8 +2451,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="29.25">
-      <c r="A13" s="55"/>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="96"/>
       <c r="B13" s="40" t="s">
         <v>26</v>
       </c>
@@ -2362,8 +2460,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15">
-      <c r="A14" s="50"/>
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="92"/>
       <c r="B14" s="19" t="s">
         <v>28</v>
       </c>
@@ -2371,8 +2469,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="29.25">
-      <c r="A15" s="50"/>
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="92"/>
       <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
@@ -2380,8 +2478,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15">
-      <c r="A16" s="50"/>
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="92"/>
       <c r="B16" s="19" t="s">
         <v>32</v>
       </c>
@@ -2389,8 +2487,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15">
-      <c r="A17" s="50"/>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="92"/>
       <c r="B17" s="19" t="s">
         <v>34</v>
       </c>
@@ -2398,8 +2496,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15">
-      <c r="A18" s="50"/>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="92"/>
       <c r="B18" s="19" t="s">
         <v>36</v>
       </c>
@@ -2407,8 +2505,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
-      <c r="A19" s="50"/>
+    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="92"/>
       <c r="B19" s="19" t="s">
         <v>38</v>
       </c>
@@ -2416,8 +2514,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15">
-      <c r="A20" s="50"/>
+    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="92"/>
       <c r="B20" s="19" t="s">
         <v>40</v>
       </c>
@@ -2425,8 +2523,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15">
-      <c r="A21" s="50"/>
+    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="92"/>
       <c r="B21" s="19" t="s">
         <v>42</v>
       </c>
@@ -2434,8 +2532,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15">
-      <c r="A22" s="56"/>
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="97"/>
       <c r="B22" s="20" t="s">
         <v>44</v>
       </c>
@@ -2443,8 +2541,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
-      <c r="A23" s="47"/>
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="83"/>
       <c r="B23" s="43" t="s">
         <v>46</v>
       </c>
@@ -2452,8 +2550,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15">
-      <c r="A24" s="48" t="s">
+    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="89" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -2463,8 +2561,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
-      <c r="A25" s="51"/>
+    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="90"/>
       <c r="B25" s="4" t="s">
         <v>51</v>
       </c>
@@ -2472,8 +2570,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15">
-      <c r="A26" s="51"/>
+    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="90"/>
       <c r="B26" s="4" t="s">
         <v>53</v>
       </c>
@@ -2481,8 +2579,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
-      <c r="A27" s="51"/>
+    <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="90"/>
       <c r="B27" s="4" t="s">
         <v>55</v>
       </c>
@@ -2490,8 +2588,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="36" customHeight="1">
-      <c r="A28" s="51"/>
+    <row r="28" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="90"/>
       <c r="B28" s="4" t="s">
         <v>57</v>
       </c>
@@ -2499,8 +2597,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
-      <c r="A29" s="51"/>
+    <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="90"/>
       <c r="B29" s="4" t="s">
         <v>59</v>
       </c>
@@ -2508,8 +2606,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
-      <c r="A30" s="51"/>
+    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="90"/>
       <c r="B30" s="4" t="s">
         <v>61</v>
       </c>
@@ -2517,8 +2615,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
-      <c r="A31" s="51"/>
+    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="90"/>
       <c r="B31" s="15" t="s">
         <v>63</v>
       </c>
@@ -2526,8 +2624,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
-      <c r="A32" s="51"/>
+    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="90"/>
       <c r="B32" s="15" t="s">
         <v>65</v>
       </c>
@@ -2535,8 +2633,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
-      <c r="A33" s="51"/>
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="90"/>
       <c r="B33" s="15" t="s">
         <v>67</v>
       </c>
@@ -2544,8 +2642,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
-      <c r="A34" s="49"/>
+    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="91"/>
       <c r="B34" s="28" t="s">
         <v>69</v>
       </c>
@@ -2553,8 +2651,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
-      <c r="A35" s="46" t="s">
+    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="82" t="s">
         <v>71</v>
       </c>
       <c r="B35" s="11" t="s">
@@ -2564,8 +2662,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
-      <c r="A36" s="50"/>
+    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="92"/>
       <c r="B36" s="14" t="s">
         <v>74</v>
       </c>
@@ -2573,8 +2671,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
-      <c r="A37" s="50"/>
+    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="92"/>
       <c r="B37" s="14" t="s">
         <v>76</v>
       </c>
@@ -2582,8 +2680,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="29.25">
-      <c r="A38" s="47"/>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="83"/>
       <c r="B38" s="12" t="s">
         <v>78</v>
       </c>
@@ -2591,8 +2689,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
-      <c r="A39" s="48" t="s">
+    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="89" t="s">
         <v>80</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -2600,8 +2698,8 @@
       </c>
       <c r="C39" s="9"/>
     </row>
-    <row r="40" spans="1:3" ht="15">
-      <c r="A40" s="51"/>
+    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="90"/>
       <c r="B40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2609,8 +2707,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
-      <c r="A41" s="49"/>
+    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="91"/>
       <c r="B41" s="8" t="s">
         <v>84</v>
       </c>
@@ -2618,8 +2716,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
-      <c r="A42" s="46" t="s">
+    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="82" t="s">
         <v>86</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -2627,8 +2725,8 @@
       </c>
       <c r="C42" s="22"/>
     </row>
-    <row r="43" spans="1:3" ht="15">
-      <c r="A43" s="50"/>
+    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="92"/>
       <c r="B43" s="14" t="s">
         <v>88</v>
       </c>
@@ -2636,8 +2734,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15">
-      <c r="A44" s="47"/>
+    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="83"/>
       <c r="B44" s="12" t="s">
         <v>90</v>
       </c>
@@ -2645,8 +2743,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="29.25">
-      <c r="A45" s="48" t="s">
+    <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="89" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -2656,8 +2754,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
-      <c r="A46" s="49"/>
+    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="91"/>
       <c r="B46" s="8" t="s">
         <v>94</v>
       </c>
@@ -2665,8 +2763,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15">
-      <c r="A47" s="46" t="s">
+    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="82" t="s">
         <v>96</v>
       </c>
       <c r="B47" s="11" t="s">
@@ -2674,8 +2772,8 @@
       </c>
       <c r="C47" s="22"/>
     </row>
-    <row r="48" spans="1:3" ht="15">
-      <c r="A48" s="47"/>
+    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="83"/>
       <c r="B48" s="12" t="s">
         <v>98</v>
       </c>
@@ -2683,8 +2781,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A49" s="48" t="s">
+    <row r="49" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="89" t="s">
         <v>100</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -2692,8 +2790,8 @@
       </c>
       <c r="C49" s="9"/>
     </row>
-    <row r="50" spans="1:3" ht="15">
-      <c r="A50" s="51"/>
+    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="90"/>
       <c r="B50" s="4" t="s">
         <v>102</v>
       </c>
@@ -2701,7 +2799,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15">
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
         <v>104</v>
       </c>
@@ -2710,7 +2808,7 @@
       </c>
       <c r="C51" s="16"/>
     </row>
-    <row r="52" spans="1:3" ht="15">
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="36" t="s">
         <v>106</v>
       </c>
@@ -2719,7 +2817,7 @@
       </c>
       <c r="C52" s="24"/>
     </row>
-    <row r="53" spans="1:3" ht="15">
+    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="31" t="s">
         <v>108</v>
       </c>
@@ -2728,7 +2826,7 @@
       </c>
       <c r="C53" s="10"/>
     </row>
-    <row r="54" spans="1:3" ht="15">
+    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="36" t="s">
         <v>110</v>
       </c>
@@ -2737,7 +2835,7 @@
       </c>
       <c r="C54" s="24"/>
     </row>
-    <row r="55" spans="1:3" ht="15">
+    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="31" t="s">
         <v>112</v>
       </c>
@@ -2746,130 +2844,130 @@
       </c>
       <c r="C55" s="10"/>
     </row>
-    <row r="56" spans="1:3" ht="15">
-      <c r="A56" s="82" t="s">
+    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="65" t="s">
         <v>114</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="83" t="s">
+      <c r="C56" s="66" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15">
-      <c r="A57" s="57" t="s">
+    <row r="57" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="59"/>
-    </row>
-    <row r="58" spans="1:3" ht="15">
-      <c r="A58" s="60" t="s">
+      <c r="C57" s="48"/>
+    </row>
+    <row r="58" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="86" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="61" t="s">
+      <c r="B58" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="62" t="s">
+      <c r="C58" s="50" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15">
-      <c r="A59" s="63"/>
+    <row r="59" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="87"/>
       <c r="B59" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C59" s="64" t="s">
+      <c r="C59" s="51" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15">
-      <c r="A60" s="63"/>
+    <row r="60" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="87"/>
       <c r="B60" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C60" s="64" t="s">
+      <c r="C60" s="51" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15">
-      <c r="A61" s="63"/>
+    <row r="61" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="87"/>
       <c r="B61" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="64" t="s">
+      <c r="C61" s="51" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15">
-      <c r="A62" s="63"/>
+    <row r="62" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="87"/>
       <c r="B62" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C62" s="64" t="s">
+      <c r="C62" s="51" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15">
-      <c r="A63" s="63"/>
+    <row r="63" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="87"/>
       <c r="B63" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C63" s="64" t="s">
+      <c r="C63" s="51" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15">
-      <c r="A64" s="65"/>
-      <c r="B64" s="66" t="s">
+    <row r="64" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="88"/>
+      <c r="B64" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="53" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15">
+    <row r="65" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="85" t="s">
+      <c r="B65" s="67" t="s">
         <v>133</v>
       </c>
       <c r="C65" s="45"/>
     </row>
-    <row r="66" spans="1:3" ht="15">
-      <c r="A66" s="86"/>
+    <row r="66" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A66" s="85"/>
       <c r="B66" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="87" t="s">
+      <c r="C66" s="68" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15">
-      <c r="A67" s="68" t="s">
+    <row r="67" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A67" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="B67" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="C67" s="70" t="s">
+      <c r="C67" s="55" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15">
-      <c r="A68" s="94"/>
-      <c r="B68" s="95" t="s">
+    <row r="68" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="79"/>
+      <c r="B68" s="75" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="96" t="s">
+      <c r="C68" s="76" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="43.5">
+    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="36" t="s">
         <v>141</v>
       </c>
@@ -2880,288 +2978,309 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15">
-      <c r="A70" s="74" t="s">
+    <row r="70" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="80" t="s">
         <v>144</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="75" t="s">
+      <c r="C70" s="59" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15">
-      <c r="A71" s="74"/>
+    <row r="71" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="80"/>
       <c r="B71" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="76" t="s">
+      <c r="C71" s="60" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15">
-      <c r="A72" s="74"/>
-      <c r="B72" s="77" t="s">
+    <row r="72" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="80"/>
+      <c r="B72" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="C72" s="78" t="s">
+      <c r="C72" s="62" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15">
-      <c r="A73" s="74"/>
-      <c r="B73" s="77" t="s">
+    <row r="73" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="80"/>
+      <c r="B73" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="C73" s="78" t="s">
+      <c r="C73" s="62" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="29.25">
-      <c r="A74" s="74"/>
-      <c r="B74" s="77" t="s">
+    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="80"/>
+      <c r="B74" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="C74" s="78" t="s">
+      <c r="C74" s="62" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15">
-      <c r="A75" s="74"/>
-      <c r="B75" s="77" t="s">
+    <row r="75" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="80"/>
+      <c r="B75" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="C75" s="78" t="s">
+      <c r="C75" s="62" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15">
-      <c r="A76" s="74"/>
-      <c r="B76" s="77" t="s">
+    <row r="76" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="80"/>
+      <c r="B76" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="78" t="s">
+      <c r="C76" s="62" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="29.25">
-      <c r="A77" s="74"/>
-      <c r="B77" s="79" t="s">
+    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="80"/>
+      <c r="B77" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="78" t="s">
+      <c r="C77" s="62" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15">
-      <c r="A78" s="74"/>
-      <c r="B78" s="77" t="s">
+    <row r="78" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A78" s="80"/>
+      <c r="B78" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="C78" s="78" t="s">
+      <c r="C78" s="62" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15">
-      <c r="A79" s="74"/>
-      <c r="B79" s="79" t="s">
+    <row r="79" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A79" s="80"/>
+      <c r="B79" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C79" s="78" t="s">
+      <c r="C79" s="62" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15">
-      <c r="A80" s="74"/>
-      <c r="B80" s="77" t="s">
+    <row r="80" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="80"/>
+      <c r="B80" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="C80" s="78" t="s">
+      <c r="C80" s="62" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15">
-      <c r="A81" s="74"/>
-      <c r="B81" s="77" t="s">
+    <row r="81" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="80"/>
+      <c r="B81" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="78" t="s">
+      <c r="C81" s="62" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15">
-      <c r="A82" s="80"/>
-      <c r="B82" s="71" t="s">
+    <row r="82" spans="1:3" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="81"/>
+      <c r="B82" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="C82" s="72" t="s">
+      <c r="C82" s="57" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15">
-      <c r="A83" s="97" t="s">
+    <row r="83" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A83" s="101" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="77" t="s">
+      <c r="B83" s="102" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="79" t="s">
+      <c r="C83" s="103" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15">
-      <c r="A84" s="98"/>
-      <c r="B84" s="77" t="s">
+    <row r="84" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A84" s="104"/>
+      <c r="B84" s="102" t="s">
         <v>172</v>
       </c>
-      <c r="C84" s="79" t="s">
+      <c r="C84" s="103" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15">
-      <c r="A85" s="98"/>
-      <c r="B85" s="77" t="s">
+    <row r="85" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A85" s="104"/>
+      <c r="B85" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="C85" s="79" t="s">
+      <c r="C85" s="103" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15">
-      <c r="A86" s="98"/>
-      <c r="B86" s="77" t="s">
+    <row r="86" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A86" s="104"/>
+      <c r="B86" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="C86" s="79" t="s">
+      <c r="C86" s="103" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15">
-      <c r="A87" s="98"/>
-      <c r="B87" s="77" t="s">
+    <row r="87" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A87" s="104"/>
+      <c r="B87" s="102" t="s">
         <v>179</v>
       </c>
-      <c r="C87" s="79" t="s">
+      <c r="C87" s="103" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15">
-      <c r="A88" s="98"/>
-      <c r="B88" s="77" t="s">
+    <row r="88" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A88" s="104"/>
+      <c r="B88" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="C88" s="101" t="s">
+      <c r="C88" s="105" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15">
-      <c r="A89" s="99"/>
-      <c r="B89" s="77" t="s">
+    <row r="89" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A89" s="104"/>
+      <c r="B89" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="C89" s="101" t="s">
+      <c r="C89" s="105" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A90" s="79"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="79"/>
-    </row>
-    <row r="91" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A91" s="79"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="79"/>
-    </row>
-    <row r="92" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A92" s="79"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="79"/>
-    </row>
-    <row r="93" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A93" s="79"/>
-      <c r="B93" s="77"/>
-      <c r="C93" s="79"/>
-    </row>
-    <row r="94" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A94" s="79"/>
-      <c r="B94" s="77"/>
-      <c r="C94" s="79"/>
-    </row>
-    <row r="95" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A95" s="79"/>
-      <c r="B95" s="77"/>
-      <c r="C95" s="79"/>
-    </row>
-    <row r="96" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A96" s="79"/>
-      <c r="B96" s="77"/>
-      <c r="C96" s="79"/>
-    </row>
-    <row r="97" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A97" s="79"/>
-      <c r="B97" s="77"/>
-      <c r="C97" s="79"/>
-    </row>
-    <row r="98" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A98" s="79"/>
-      <c r="B98" s="77"/>
-      <c r="C98" s="79"/>
-    </row>
-    <row r="99" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A99" s="79"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79"/>
-    </row>
-    <row r="100" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A100" s="79"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79"/>
-    </row>
-    <row r="101" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A101" s="79"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79"/>
-    </row>
-    <row r="102" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A102" s="79"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="79"/>
-    </row>
-    <row r="103" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A103" s="79"/>
-      <c r="B103" s="77"/>
-      <c r="C103" s="79"/>
-    </row>
-    <row r="104" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A104" s="79"/>
-      <c r="B104" s="77"/>
-      <c r="C104" s="79"/>
-    </row>
-    <row r="105" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A105" s="79"/>
-      <c r="B105" s="77"/>
-      <c r="C105" s="79"/>
-    </row>
-    <row r="106" spans="1:3" ht="39.75" customHeight="1">
+    <row r="90" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="104"/>
+      <c r="B90" s="106" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="103" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A91" s="104"/>
+      <c r="B91" s="107"/>
+      <c r="C91" s="103" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="104"/>
+      <c r="B92" s="107"/>
+      <c r="C92" s="103" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A93" s="104"/>
+      <c r="B93" s="107"/>
+      <c r="C93" s="103" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A94" s="104"/>
+      <c r="B94" s="107"/>
+      <c r="C94" s="103" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="104"/>
+      <c r="B95" s="107"/>
+      <c r="C95" s="108" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="98" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" s="99" t="s">
+        <v>205</v>
+      </c>
+      <c r="C96" s="100" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="64"/>
+      <c r="B97" s="69"/>
+      <c r="C97" s="64"/>
+    </row>
+    <row r="98" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="63"/>
+      <c r="B98" s="61"/>
+      <c r="C98" s="63"/>
+    </row>
+    <row r="99" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="63"/>
+      <c r="B99" s="61"/>
+      <c r="C99" s="63"/>
+    </row>
+    <row r="100" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="63"/>
+      <c r="B100" s="61"/>
+      <c r="C100" s="63"/>
+    </row>
+    <row r="101" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="63"/>
+      <c r="B101" s="61"/>
+      <c r="C101" s="63"/>
+    </row>
+    <row r="102" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="63"/>
+      <c r="B102" s="61"/>
+      <c r="C102" s="63"/>
+    </row>
+    <row r="103" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="63"/>
+      <c r="B103" s="61"/>
+      <c r="C103" s="63"/>
+    </row>
+    <row r="104" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="63"/>
+      <c r="B104" s="61"/>
+      <c r="C104" s="63"/>
+    </row>
+    <row r="105" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="63"/>
+      <c r="B105" s="61"/>
+      <c r="C105" s="63"/>
+    </row>
+    <row r="106" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="37"/>
       <c r="B106" s="38"/>
       <c r="C106" s="37"/>
     </row>
-    <row r="107" spans="1:3" ht="39.75" customHeight="1">
+    <row r="107" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="37"/>
       <c r="B107" s="38"/>
       <c r="C107" s="37"/>
     </row>
-    <row r="108" spans="1:3" ht="39.75" customHeight="1">
+    <row r="108" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="37"/>
       <c r="B108" s="38"/>
       <c r="C108" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A83:A89"/>
+  <mergeCells count="17">
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="A83:A95"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A70:A82"/>
     <mergeCell ref="A2:A3"/>
@@ -3189,14 +3308,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08591C4C-90F4-43C8-ABF7-6AFD4C29F491}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="39.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.5703125" style="17" customWidth="1"/>
     <col min="2" max="2" width="89.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="122.42578125" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="39.75" customHeight="1">
+    <row r="1" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3207,16 +3326,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A2" s="89" t="s">
+    <row r="2" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="71" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="91"/>
-    </row>
-    <row r="3" spans="1:3" ht="64.5" customHeight="1">
+      <c r="C2" s="72"/>
+    </row>
+    <row r="3" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>141</v>
       </c>
@@ -3227,36 +3346,36 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A4" s="89" t="s">
+    <row r="4" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="91"/>
-    </row>
-    <row r="5" spans="1:3" ht="39.75" customHeight="1">
+      <c r="C4" s="72"/>
+    </row>
+    <row r="5" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="58" t="s">
         <v>190</v>
       </c>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A6" s="89" t="s">
+    <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="70" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="73" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="72" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="54.75" customHeight="1">
+    <row r="7" spans="1:3" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>194</v>
       </c>
@@ -3267,122 +3386,122 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="81"/>
-    </row>
-    <row r="9" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A9" s="79"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="79"/>
-    </row>
-    <row r="10" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="79"/>
-    </row>
-    <row r="11" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="79"/>
-    </row>
-    <row r="12" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A12" s="79"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="79"/>
-    </row>
-    <row r="13" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A13" s="79"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="79"/>
-    </row>
-    <row r="14" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A14" s="79"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="79"/>
-    </row>
-    <row r="15" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A15" s="79"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="79"/>
-    </row>
-    <row r="16" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A16" s="79"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="79"/>
-    </row>
-    <row r="17" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A17" s="79"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="79"/>
-    </row>
-    <row r="18" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A18" s="79"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="79"/>
-    </row>
-    <row r="19" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A19" s="79"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="79"/>
-    </row>
-    <row r="20" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A20" s="79"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="79"/>
-    </row>
-    <row r="21" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A21" s="79"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="79"/>
-    </row>
-    <row r="22" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A22" s="79"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="79"/>
-    </row>
-    <row r="23" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A23" s="79"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="79"/>
-    </row>
-    <row r="24" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A24" s="79"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="79"/>
-    </row>
-    <row r="25" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A25" s="79"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="79"/>
-    </row>
-    <row r="26" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A26" s="79"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="79"/>
-    </row>
-    <row r="27" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A27" s="79"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="79"/>
-    </row>
-    <row r="28" spans="1:3" ht="39.75" customHeight="1">
-      <c r="A28" s="79"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="79"/>
-    </row>
-    <row r="29" spans="1:3" ht="39.75" customHeight="1">
+    <row r="8" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="64"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="64"/>
+    </row>
+    <row r="9" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="63"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="63"/>
+    </row>
+    <row r="10" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="63"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="63"/>
+    </row>
+    <row r="11" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="63"/>
+    </row>
+    <row r="12" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="63"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="63"/>
+    </row>
+    <row r="13" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="63"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="63"/>
+    </row>
+    <row r="14" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="63"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="63"/>
+    </row>
+    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="63"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="63"/>
+    </row>
+    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="63"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="63"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="63"/>
+    </row>
+    <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="63"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="63"/>
+    </row>
+    <row r="19" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="63"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="63"/>
+    </row>
+    <row r="20" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="63"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="63"/>
+    </row>
+    <row r="21" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="63"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="63"/>
+    </row>
+    <row r="22" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="63"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="63"/>
+    </row>
+    <row r="23" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="63"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="63"/>
+    </row>
+    <row r="24" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="63"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="63"/>
+    </row>
+    <row r="25" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="63"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="63"/>
+    </row>
+    <row r="26" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="63"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="63"/>
+    </row>
+    <row r="27" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="63"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="63"/>
+    </row>
+    <row r="28" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="63"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="63"/>
+    </row>
+    <row r="29" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37"/>
       <c r="B29" s="38"/>
       <c r="C29" s="37"/>
     </row>
-    <row r="30" spans="1:3" ht="39.75" customHeight="1">
+    <row r="30" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37"/>
       <c r="B30" s="38"/>
       <c r="C30" s="37"/>
     </row>
-    <row r="31" spans="1:3" ht="39.75" customHeight="1">
+    <row r="31" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="37"/>
       <c r="B31" s="38"/>
       <c r="C31" s="37"/>
